--- a/master/result/42_穿越未来_赛博世界的女王/42_穿越未来_赛博世界的女王.xlsx
+++ b/master/result/42_穿越未来_赛博世界的女王/42_穿越未来_赛博世界的女王.xlsx
@@ -397,577 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sky</v>
       </c>
       <c r="B2" t="str">
-        <v>sky</v>
+        <v>/sky/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>天空</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>cyberspace</v>
       </c>
       <c r="B3" t="str">
-        <v>cyberspace</v>
+        <v>/cyberspace/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>虚拟信息空间</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>circumference</v>
       </c>
       <c r="B4" t="str">
-        <v>circumference</v>
+        <v>/circumference/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>圆周</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>disc</v>
       </c>
       <c r="B5" t="str">
-        <v>disc</v>
+        <v>/disc/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>圆盘</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>fall</v>
       </c>
       <c r="B6" t="str">
-        <v>fall</v>
+        <v>/fɔːl/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>跌倒</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>database</v>
       </c>
       <c r="B7" t="str">
-        <v>database</v>
+        <v>/database/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>数据库</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>maintain</v>
       </c>
       <c r="B8" t="str">
-        <v>maintain</v>
+        <v>/meɪnˈteɪn/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>维持</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>tramp</v>
       </c>
       <c r="B9" t="str">
-        <v>tramp</v>
+        <v>/tramp/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>步行</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>team</v>
       </c>
       <c r="B10" t="str">
-        <v>team</v>
+        <v>/team/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>小组</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>political</v>
       </c>
       <c r="B11" t="str">
-        <v>political</v>
+        <v>/political/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>政治的</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>delegate</v>
       </c>
       <c r="B12" t="str">
-        <v>delegate</v>
+        <v>/delegate/</v>
       </c>
       <c r="C12" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D12" t="str">
         <v>代表</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>framework</v>
       </c>
       <c r="B13" t="str">
-        <v>framework</v>
+        <v>/framework/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>框架</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>advanced</v>
       </c>
       <c r="B14" t="str">
-        <v>advanced</v>
+        <v>/ədˈvɑːnst/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>高级的</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>silicon</v>
       </c>
       <c r="B15" t="str">
-        <v>silicon</v>
+        <v>/silicon/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>硅</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>take</v>
       </c>
       <c r="B16" t="str">
-        <v>take</v>
+        <v>/teɪk/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>拿取</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>arithmetic</v>
       </c>
       <c r="B17" t="str">
-        <v>arithmetic</v>
+        <v>/arithmetic/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>算术</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>significant</v>
       </c>
       <c r="B18" t="str">
-        <v>significant</v>
+        <v>/significant/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>重大的</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>pulse</v>
       </c>
       <c r="B19" t="str">
-        <v>pulse</v>
+        <v>/pulse/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>脉搏</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>therapy</v>
       </c>
       <c r="B20" t="str">
-        <v>therapy</v>
+        <v>/therapy/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>治疗</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>skin</v>
       </c>
       <c r="B21" t="str">
-        <v>skin</v>
+        <v>/skin/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>皮肤</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>acrobat</v>
       </c>
       <c r="B22" t="str">
-        <v>acrobat</v>
+        <v>/acrobat/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>特技演员</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>explore</v>
       </c>
       <c r="B23" t="str">
-        <v>explore</v>
+        <v>/ɪkˈsplɔː/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>探索</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>trunk</v>
       </c>
       <c r="B24" t="str">
-        <v>trunk</v>
+        <v>/trunk/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>大衣箱</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>abuse</v>
       </c>
       <c r="B25" t="str">
-        <v>abuse</v>
+        <v>/abuse/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>滥用</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>brook</v>
       </c>
       <c r="B26" t="str">
-        <v>brook</v>
+        <v>/brook/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>小溪</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>touch</v>
       </c>
       <c r="B27" t="str">
-        <v>touch</v>
+        <v>/tʌtʃ/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>触</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>model</v>
       </c>
       <c r="B28" t="str">
-        <v>model</v>
+        <v>/model/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>模型</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>within</v>
       </c>
       <c r="B29" t="str">
-        <v>within</v>
+        <v>/within/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>在...里面</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>three</v>
       </c>
       <c r="B30" t="str">
-        <v>three</v>
+        <v>/three/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>三</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>margin</v>
       </c>
       <c r="B31" t="str">
-        <v>margin</v>
+        <v>/margin/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>页边空白</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>my</v>
       </c>
       <c r="B32" t="str">
-        <v>my</v>
+        <v>/my/</v>
       </c>
       <c r="C32" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>我的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>useful</v>
       </c>
       <c r="B33" t="str">
-        <v>useful</v>
+        <v>/useful/</v>
       </c>
       <c r="C33" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>有用的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>sympathetic</v>
       </c>
       <c r="B34" t="str">
-        <v>sympathetic</v>
+        <v>/sympathetic/</v>
       </c>
       <c r="C34" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D34" t="str">
         <v>有同情心的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>bean</v>
       </c>
       <c r="B35" t="str">
-        <v>bean</v>
+        <v>/biːn/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>豆</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>suffice</v>
       </c>
       <c r="B36" t="str">
-        <v>suffice</v>
+        <v>/suffice/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>充足</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>Negro</v>
       </c>
       <c r="B37" t="str">
-        <v>Negro</v>
+        <v>/Negro/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>黑人</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>medium</v>
       </c>
       <c r="B38" t="str">
-        <v>medium</v>
+        <v>/medium/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>媒体</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>hire</v>
       </c>
       <c r="B39" t="str">
-        <v>hire</v>
+        <v>/haɪə/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>雇用</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>preference</v>
       </c>
       <c r="B40" t="str">
-        <v>preference</v>
+        <v>/preference/</v>
       </c>
       <c r="C40" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>偏爱</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>confer</v>
       </c>
       <c r="B41" t="str">
-        <v>confer</v>
+        <v>/confer/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>商讨</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>sunshine</v>
       </c>
       <c r="B42" t="str">
-        <v>sunshine</v>
+        <v>/sunshine/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>日光</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>drip</v>
       </c>
       <c r="B43" t="str">
-        <v>drip</v>
+        <v>/drip/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>滴下</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>replace</v>
       </c>
       <c r="B44" t="str">
-        <v>replace</v>
+        <v>/rɪˈpleɪs/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>取代</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>longitude</v>
       </c>
       <c r="B45" t="str">
-        <v>longitude</v>
+        <v>/longitude/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>经度</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>absurd</v>
       </c>
       <c r="B46" t="str">
-        <v>absurd</v>
+        <v>/absurd/</v>
       </c>
       <c r="C46" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D46" t="str">
         <v>荒谬的</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>unfortunately</v>
       </c>
       <c r="B47" t="str">
-        <v>unfortunately</v>
+        <v>/unfortunately/</v>
       </c>
       <c r="C47" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D47" t="str">
         <v>不幸地</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>heel</v>
       </c>
       <c r="B48" t="str">
-        <v>heel</v>
+        <v>/heel/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>脚后跟</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>timely</v>
       </c>
       <c r="B49" t="str">
-        <v>timely</v>
+        <v>/timely/</v>
       </c>
       <c r="C49" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>及时的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>convenience</v>
       </c>
       <c r="B50" t="str">
-        <v>convenience</v>
+        <v>/kənˈviːniəns/</v>
       </c>
       <c r="C50" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>便利</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>die</v>
       </c>
       <c r="B51" t="str">
-        <v>die</v>
+        <v>/daɪ/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>死亡</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>